--- a/YouTube이슈분석_개인채널_2026-07-23.xlsx
+++ b/YouTube이슈분석_개인채널_2026-07-23.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="106">
   <si>
     <t>날짜</t>
   </si>
@@ -80,22 +80,25 @@
     <t>사건사고</t>
   </si>
   <si>
-    <t>114년째 미제로 남은 미국 최악의 밀실 살인사건 [사건사고]</t>
+    <t>최근 폴란드를 충격에 빠트린 '고스틴 카르텔'의 전말 [사건사고]</t>
   </si>
   <si>
     <t>기묘한 밤</t>
   </si>
   <si>
-    <t>2026-07-16</t>
-  </si>
-  <si>
-    <t>11:35</t>
-  </si>
-  <si>
-    <t>본 영상은 114년 동안 해결되지 않은 미국 역사상 가장 충격적인 밀실 살인사건을 다룹니다. 사건의 기이한 정황과 철저한 폐쇄성으로 인해 범인의 흔적조차 찾지 못한 채 오늘날까지 미스터리로 남아있는 사건의 전말과 그 배경을 심도 있게 분석한 영상입니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 자극적인 소재의 미제 사건을 다루는 영상이므로 사실 관계 확인이 필요할 수 있습니다.</t>
+    <t>2026-07-22</t>
+  </si>
+  <si>
+    <t>8:55</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>본 영상은 폴란드에서 발생한 '고스틴 카르텔' 사건을 다룹니다. 깨끗한 우유 제품이라는 소비자의 신뢰 뒤에 숨겨진 불투명한 생산 과정과 부정부패의 실체를 파헤치며, 대기업과 카르텔이 결탁해 시장을 교란하고 소비자를 기만한 충격적인 사건의 전말을 상세히 추적합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 해당 영상은 실제 사건의 심각성을 자극적으로 강조하는 클릭베이트 형식의 콘텐츠이므로 객관적인 사실 확인을 병행하는 것이 좋습니다.</t>
   </si>
   <si>
     <t>▶</t>
@@ -104,22 +107,22 @@
     <t>메타데이터+자막(Gemini)</t>
   </si>
   <si>
-    <t>최근 폴란드를 충격에 빠트린 '고스틴 카르텔'의 전말 [사건사고]</t>
-  </si>
-  <si>
-    <t>2026-07-22</t>
-  </si>
-  <si>
-    <t>8:55</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>이 영상은 폴란드를 뒤흔든 '고스틴 카르텔' 사건을 다룹니다. 우유라는 일상적인 식품의 생산 과정에서 벌어진 불투명한 유통 구조와 카르텔의 실체를 파헤치며, 소비자들의 신뢰를 저버린 기업들의 부도덕한 행태와 그로 인해 발생한 사회적 충격을 심도 있게 분석하고 있습니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 자극적인 제목과 썸네일로 클릭을 유도하는 콘텐츠이므로 사실관계 확인이 필요합니다.</t>
+    <t>[사건사고] 야쿠자에게 20억을 빌린 남자, 그 결말은...? 타카하시 요시히로 사건</t>
+  </si>
+  <si>
+    <t>괴미사</t>
+  </si>
+  <si>
+    <t>2026-07-21</t>
+  </si>
+  <si>
+    <t>12:21</t>
+  </si>
+  <si>
+    <t>1992년 발생한 타카하시 요시히로 사건을 다룬 영상입니다. 경제적 어려움에 처한 타카하시가 야쿠자로부터 거액인 20억 원을 빌린 뒤, 이를 갚지 못하고 결국 극단적인 범행을 저지르게 된 배경과 수사 과정 및 체포까지의 비극적인 사건 전말을 추적합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 자극적인 소재를 다루고 있으므로 강력 범죄에 거부감이 있는 시청자는 주의가 필요합니다.</t>
   </si>
   <si>
     <t>【일사사】 일본 15년 차 간호사는 왜 환자의 수액에 대변을 넣었나 | 일본 간호사 "대변" 살인 혐의 사건</t>
@@ -128,16 +131,34 @@
     <t>테가미 | 일본 사건사고</t>
   </si>
   <si>
-    <t>2026-07-21</t>
-  </si>
-  <si>
     <t>10:38</t>
   </si>
   <si>
-    <t>2026년 1월 일본 치바현의 한 병원에서 입원 중이던 75세 환자의 수액에 대변이 주입되어 환자가 패혈증으로 사망한 사건을 다룹니다. 당시 야간 책임 간호사였던 후루카와 미유키가 살인 혐의로 체포되었으나 혐의를 부인하고 있어 사회적 충격을 주고 있습니다. 본 영상은 사건의 경위와 수사 과정, 범행 동기 등을 차분하게 분석하며 병원 내 안전 관리와 간호사의 직업윤리 문제를 제기합니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 자극적인 소재의 사건사고를 다루고 있으므로 감정적인 시청보다는 사건의 본질과 재발 방지 대책에 주목해 시청하시길 권장합니다.</t>
+    <t>2026년 1월 일본 치바현의 한 병원에서 입원 중이던 75세 환자의 수액관에 대변이 혼입되어 환자가 패혈증으로 사망한 충격적인 사건입니다. 당시 야간 책임 간호사였던 후루카와 미유키가 살인 혐의로 체포되었으나 현재 혐의를 강력히 부인하고 있어, 일본 사회에 큰 충격과 논란을 일으키고 있는 사건의 전말과 수사 과정을 정리했습니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 자극적인 범죄 소재를 다룬 영상이므로 시청 시 정서적 주의가 필요합니다.</t>
+  </si>
+  <si>
+    <t>일본</t>
+  </si>
+  <si>
+    <t>【栃木闇バイト強盗殺人】紹介しただけでも逆送、家裁が下した厳しい判断【かなえ先生の切り抜き】元配信2026/07/18</t>
+  </si>
+  <si>
+    <t>【公認】かなえ先生への共感【Vtuber】</t>
+  </si>
+  <si>
+    <t>2026-07-20</t>
+  </si>
+  <si>
+    <t>15:38</t>
+  </si>
+  <si>
+    <t>본 영상은 토치기현에서 발생한 어둠의 아르바이트 강도 살인 사건을 다룹니다. 가해자 소년들이 단순 가담이나 소개만으로도 엄중한 처벌을 받는 현실을 짚어내며, 소년법의 한계와 범죄의 잔혹성, 그리고 가담한 소년들의 비극적인 결말을 범죄학적 관점에서 상세히 분석하여 경각심을 고취합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 소셜 미디어를 통한 고수익 아르바이트 제안은 범죄 연루 가능성이 매우 높으니 절대 현혹되지 않도록 주의해야 합니다.</t>
   </si>
   <si>
     <t>미국</t>
@@ -146,6 +167,21 @@
     <t>핫이슈</t>
   </si>
   <si>
+    <t>Trans Person Goes NUCLEAR on Cops for being Misgendered!</t>
+  </si>
+  <si>
+    <t>Tyrone Magnus</t>
+  </si>
+  <si>
+    <t>15:08</t>
+  </si>
+  <si>
+    <t>플로리다 대학교 캠퍼스에서 27세 트랜스젠더 학생 재럿 빅이 경찰관의 성별 호칭 실수를 문제 삼으며 격렬하게 항의하다 체포되는 사건을 다룹니다. 해당 학생은 경찰관의 대응에 극도로 흥분하여 고성을 지르며 대치했으며, 이 과정이 바디캠에 고스란히 담겨 온라인상에서 큰 논란과 화제를 불러일으켰습니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 자극적인 갈등 상황을 강조하여 조회수를 유도하는 클릭베이트성 콘텐츠이므로, 사건의 맥락을 객관적으로 파악하려는 시각이 필요합니다.</t>
+  </si>
+  <si>
     <t>VIRAL!! KOMEN FANS FILIPINA YANG TIDAK TERIMA DIKALAHKAN INDONESIA 3-0 DI KANDANG SENDIRI SEA V CUP</t>
   </si>
   <si>
@@ -158,10 +194,10 @@
     <t>10:12</t>
   </si>
   <si>
-    <t>2026 SEA V League 남자 배구 대회에서 인도네시아 국가대표팀이 필리핀을 상대로 원정 경기임에도 불구하고 3-0 완승을 거두었습니다. 이 승리로 인도네시아는 조 1위를 확정 지으며 준결승에서 베트남과 맞붙게 되었습니다. 필리핀 홈 관중들 사이에서 나온 아쉬운 반응들이 화제가 되고 있습니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 제목과 달리 실제 영상 내용은 일반적인 경기 요약이며, 자극적인 제목을 이용한 조회수 유도성 콘텐츠일 수 있으니 주의하세요.</t>
+    <t>2026년 SEA V리그 대회에서 인도네시아 남자 배구 대표팀이 필리핀을 상대로 3-0 완승을 거두었습니다. 이번 승리로 인도네시아는 조 1위를 확정 지었으며, 준결승전에서 베트남과 맞붙게 되었습니다. 필리핀 홈구장에서 이뤄낸 압도적인 성과로 현지 팬들 사이에서 큰 화제를 모으고 있습니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 자극적인 제목과 달리 실제 내용은 단순한 경기 결과 보도이므로 정보성 확인 위주로 시청하시기 바랍니다.</t>
   </si>
   <si>
     <t>Black People Are Finally Fighting Back... And Some People Can't Handle It</t>
@@ -170,16 +206,13 @@
     <t>Kelvin decoded</t>
   </si>
   <si>
-    <t>2026-07-20</t>
-  </si>
-  <si>
     <t>19:03</t>
   </si>
   <si>
-    <t>본 영상은 최근 SNS에서 화제가 된 흑인들이 부당한 대우에 침묵하지 않고 적극적으로 대응하는 영상들을 분석합니다. 영상 속 사례들을 통해 인종적 편견, 존중, 책임이라는 주제를 다루며, 이러한 대응이 정당한 자기방어인지 혹은 불필요한 갈등 확산인지에 대해 시청자들의 판단을 묻는 토론 형식의 콘텐츠입니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 자극적인 화제를 활용해 시청자의 감정을 유도하는 클릭베이트 형식의 콘텐츠이므로, 영상의 주관적 견해를 비판적으로 수용하는 것이 좋습니다.</t>
+    <t>본 영상은 최근 소셜 미디어에서 화제가 된 흑인들의 부당한 처우에 대한 저항 사례들을 다룹니다. 영상은 당사자들이 침묵하지 않고 자신의 권리를 주장하는 장면들을 분석하며, 이것이 정당한 자기방어인지 혹은 불필요한 갈등 확산인지에 대해 인종 차별, 책임, 존중이라는 사회적 관점에서 심도 있는 논의를 이끌어냅니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 자극적인 제목과 클릭베이트 형식을 띠고 있으므로, 실제 사례를 볼 때 감정적인 대응보다 영상이 제시하는 맥락을 비판적으로 파악하는 것이 중요합니다.</t>
   </si>
   <si>
     <t>Defense Attorney Reveals What Could BLOW the Nolan Wells Case WIDE OPEN</t>
@@ -191,124 +224,115 @@
     <t>18:48</t>
   </si>
   <si>
-    <t>이 영상은 미시시피주 혼 아일랜드에서 사망한 18세 운동선수 놀란 자비에 웰스 사건을 다룹니다. 채널 운영자는 유명 변호사와의 인터뷰를 통해 주류 언론이 보도하지 않는 사건의 이면과 잠재적인 법적 전략, 수사의 핵심 변수가 될 수 있는 결정적 단서들을 분석하며 사건의 진실을 파헤칩니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 자극적인 문구로 시청을 유도하는 클릭베이트 형식의 영상이므로, 객관적인 수사 기록이나 신뢰할 수 있는 공식 보도와 교차 검증하는 것이 좋습니다.</t>
-  </si>
-  <si>
-    <t>Lil Durk Just Took a Huge W in Court</t>
-  </si>
-  <si>
-    <t>BlackySpeakz</t>
-  </si>
-  <si>
-    <t>10:56</t>
-  </si>
-  <si>
-    <t>릴 더크(Lil Durk)가 연루된 청부 살인 사건에서 판사가 검찰의 추가 혐의 병합 시도를 기각하며 더크가 법적 승리를 거두었습니다. 본 영상은 이번 판결의 의미와 검찰의 전략 변화, 그리고 LA 사건의 향후 전망을 다룹니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 자극적인 썸네일과 달리 사건의 구체적인 법적 절차 변화에 집중한 분석 영상이므로 실제 재판 진행 상황을 이해하는 데 유용합니다.</t>
-  </si>
-  <si>
-    <t>Ừ Thì Xe Phần 415 : Uống cà phê vào thì đỡ lao lên vỉa hè | @uthixe​</t>
-  </si>
-  <si>
-    <t>Ừ Thì Xe</t>
-  </si>
-  <si>
-    <t>2026-07-18</t>
-  </si>
-  <si>
-    <t>15:30</t>
-  </si>
-  <si>
-    <t>본 영상은 베트남의 교통 상황을 다루는 'Ừ Thì Xe' 채널의 415번째 에피소드입니다. 실제 도로에서 발생하는 황당하고 위험한 운전 사례들을 모아 보여주며, 이를 통해 교통 안전 의식을 고취합니다. 유머러스한 해설을 곁들여 운전자가 도로 위에서 저지를 수 있는 실수와 사고 방지 방법을 현실적으로 전달하는 교육 겸 엔터테인먼트 콘텐츠입니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 도로 위 돌발 상황은 언제 어디서든 발생할 수 있으므로, 항상 방어 운전을 실천하고 주변 차량의 움직임을 예의주시해야 합니다.</t>
+    <t>이 영상은 미시시피주 혼 아일랜드에서 사망한 18세 운동선수 놀란 자비에르 웰스 사건을 다룹니다. 채널 운영자는 유명 형사 전문 변호사와의 대담을 통해 주류 언론이 간과하고 있는 이 사건의 숨겨진 법적 전략과 수사상의 핵심 쟁점들을 심층적으로 분석하며, 사건의 판도를 바꿀 수 있는 새로운 관점을 제시합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 클릭베이트 성격이 강한 영상이므로, 언론의 일반적인 보도와 전문가의 추측성 분석을 구분하여 비판적으로 수용해야 합니다.</t>
+  </si>
+  <si>
+    <t>Lawlessness In Ireland ! Why Are We Ignoring This??</t>
+  </si>
+  <si>
+    <t>Derek Domino</t>
+  </si>
+  <si>
+    <t>11:16</t>
+  </si>
+  <si>
+    <t>아일랜드 캐번주 버지니아에서 발생한 청소년 집단 난동 사건을 다룹니다. 라모어 호수 인근에서 시작된 폭력 사태가 도심까지 확산되어 다수의 부상자가 발생했고 경찰이 수사에 착수했습니다. 칼을 동원한 공격 정황 등 온라인상의 여러 의혹과 영상 속 진실을 분석하며, 지역 사회의 치안 부재 문제를 강하게 비판합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 자극적인 썸네일과 제목을 사용한 개인의 의견 중심 콘텐츠이므로, 확정되지 않은 소문과 공식 뉴스 보도를 명확히 구분하여 시청하시기 바랍니다.</t>
+  </si>
+  <si>
+    <t>Racist Goes Viral for MOCKING Nolan Wells... Then Pays the Price</t>
+  </si>
+  <si>
+    <t>11:47</t>
+  </si>
+  <si>
+    <t>본 영상은 놀란 웰스 사건을 조롱하여 사회적 공분을 산 레밍턴 레인 맥콜의 사례를 다룹니다. 그는 자신의 인종차별적 언행으로 직장에서 해고되는 등 혹독한 대가를 치렀으며, 이후 피해자 행세를 하며 크라우드 펀딩으로 이득을 보려 시도했습니다. 영상은 이러한 악질적인 인터넷 문화와 논란을 이용해 수익을 창출하려는 잘못된 경향성을 비판적으로 분석합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 자극적인 범죄 사건이나 이슈를 이용해 모금 활동을 벌이는 경우, 검증되지 않은 크라우드 펀딩에 주의해야 합니다.</t>
   </si>
   <si>
     <t>라이징스타</t>
   </si>
   <si>
-    <t>S8UL Goldy Breaks Silence | Scout angry reaction on Kaashvi vs thug matter</t>
-  </si>
-  <si>
-    <t>ACE eSports Insiders</t>
-  </si>
-  <si>
-    <t>9:56</t>
-  </si>
-  <si>
-    <t>이 영상은 인도 게이밍 커뮤니티 내 S8UL의 Goldy가 Kaashvi와 Thug 사이의 갈등 논란에 대해 침묵을 깨고 입장을 밝힌 내용과, 이에 대한 Scout의 분노 섞인 반응을 다룹니다. 커뮤니티 내부의 갈등과 인플루언서들의 반응을 중점적으로 조명하며 관련 소식을 전달합니다.</t>
-  </si>
-  <si>
-    <t>⚠️해당 영상은 자극적인 갈등을 소재로 한 클릭베이트 성격이 강하므로, 정보의 사실 여부를 공식 채널을 통해 반드시 교차 확인하시기 바랍니다.</t>
-  </si>
-  <si>
-    <t>일본</t>
-  </si>
-  <si>
-    <t>山本由伸の完投で矢田先生に弟子入りが殺到！「異常だよ」投手コーチが語ったド軍内部の光景とは？【海外の反応/MLB/メジャー/野球】</t>
-  </si>
-  <si>
-    <t>JAPAN PRIDE SPORTS【海外の反応】</t>
-  </si>
-  <si>
-    <t>18:42</t>
-  </si>
-  <si>
-    <t>본 영상은 LA 다저스의 야마모토 요시노부가 완투승을 거둔 후, 투수 코치 야다 선생의 지도법이 주목받으며 구단 내부에서 큰 화제가 된 상황을 다룹니다. 해외 매체와 팬들이 야마모토의 기량 향상과 일본식 투구 훈련의 효과에 대해 보인 놀라운 반응들을 소개하며, 그가 메이저리그 무대에서 성공적으로 적응하고 있음을 집중 조명합니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 본 영상은 다소 과장된 클릭베이트성 제목을 포함하고 있으므로, 일본 선수의 활약상 위주로 가볍게 시청하는 것이 좋습니다.</t>
-  </si>
-  <si>
-    <t>【海外の反応】空調服を初めて着た外国人…わずか10分で手放せなくなった理由とは？</t>
-  </si>
-  <si>
-    <t>日本称賛【 海外の反応】</t>
-  </si>
-  <si>
-    <t>11:33</t>
-  </si>
-  <si>
-    <t>일본의 독창적인 발명품인 '공조복'이 기록적인 폭염을 겪는 유럽 및 미국 등 해외에서 큰 화제입니다. 처음엔 옷에 선풍기가 달린 것을 의아해하던 외국인들이 10분 만에 그 쾌적함과 실용성에 매료되어, 열사병 예방과 무더위 대책으로 필수적인 기술이라며 자국 도입을 강력히 희망하는 반응을 보이고 있습니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 일본의 아이디어 상품이 전 세계 폭염 대응의 혁신적 해결책으로 주목받고 있음을 보여주는 사례입니다.</t>
-  </si>
-  <si>
-    <t>【大谷翔平】ベッツ200号達成を試合後に祝福…大谷が企画したサプライズ食事会をフリーマンが振り返り話題【海外の反応 MLBメジャー 野球】</t>
-  </si>
-  <si>
-    <t>大谷応援ファンズ</t>
-  </si>
-  <si>
-    <t>20:21</t>
-  </si>
-  <si>
-    <t>이 영상은 오타니 쇼헤이가 팀 동료 무키 베츠의 통산 200호 홈런 달성을 축하하기 위해 직접 기획한 깜짝 회식의 비하인드 스토리를 다룹니다. 선수단 전원을 비밀리에 소집하여 화기애애한 분위기 속에서 팀의 결속력을 다진 에피소드를 프리먼과 로버츠 감독의 인터뷰를 통해 소개하며, 다저스 내 오타니의 리더십과 동료애를 조명합니다.</t>
-  </si>
-  <si>
-    <t>⚠️해당 채널은 오타니 쇼헤이 팬 채널로, 공식 뉴스보다는 팬심이 반영된 감성적인 편집이 가미되어 있을 수 있습니다.</t>
-  </si>
-  <si>
-    <t>【海外の反応】「日本人のせいで母国に帰れない…」子供を連れて行った海外ママが言葉を失った理由とは...</t>
-  </si>
-  <si>
-    <t>福ちゃんねる【海外の反応】</t>
-  </si>
-  <si>
-    <t>15:36</t>
-  </si>
-  <si>
-    <t>본 영상은 일본에 방문한 외국인 엄마가 일본의 안전함과 배려 깊은 문화에 감동받아 본국으로 돌아가기 싫어질 정도의 경험을 했다는 에피소드를 다룹니다. 일본인들의 친절함과 사회적 질서가 외국인들에게 어떻게 특별한 감동을 주는지, 그들의 관점에서 일본의 매력을 조명하는 콘텐츠입니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 자극적인 제목과 클릭베이트 형식을 사용하여 시청자의 호기심을 유도하는 채널이므로, 내용의 객관적 사실 여부를 비판적으로 확인하며 시청하는 것이 좋습니다.</t>
+    <t>【海外の反応】「高市首相は一体何をした？！」日本に向かう10隻のタンカーに海外が驚愕した理由</t>
+  </si>
+  <si>
+    <t>すごいJAPAN【海外の反応】</t>
+  </si>
+  <si>
+    <t>18:50</t>
+  </si>
+  <si>
+    <t>이 영상은 일본의 고이치 사나에가 총리가 된 상황을 가정하고, 일본으로 향하는 10척의 유조선과 에너지 안보 정책에 대한 해외 반응을 다룹니다. 일본의 자원 확보 전략과 에너지 독립 가능성에 대해 외국인들의 긍정적인 평가와 놀라움을 엮어낸 전형적인 국뽕 소재의 콘텐츠입니다.</t>
+  </si>
+  <si>
+    <t>⚠️이 영상은 자극적인 제목을 사용한 전형적인 국뽕(클릭베이트) 콘텐츠이므로, 사실관계 확인보다는 일본 내의 국수주의적 여론 경향을 파악하는 용도로만 시청하는 것이 좋습니다.</t>
+  </si>
+  <si>
+    <t>HUMAN TETRIS x 2 Player Co-op 💕 | Viral Challenge | High-Quality Immersive Interactive Warm-Up #6</t>
+  </si>
+  <si>
+    <t>TetraPeng</t>
+  </si>
+  <si>
+    <t>4:40</t>
+  </si>
+  <si>
+    <t>이 영상은 '휴먼 테트리스' 챌린지를 2인 협동 모드로 즐기는 과정을 담고 있습니다. 기존의 지루한 준비 운동 방식에서 벗어나, 파트너와 함께 벽의 모양에 맞춰 유연한 포즈를 취하며 높은 몰입감을 경험하는 인터랙티브 콘텐츠입니다. 팀워크와 신체 유연성이 핵심이며, 누구나 즐겁게 따라 할 수 있는 재미있는 도전 형태를 보여줍니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 실제 신체 활동이 포함된 도전이므로, 관절이나 근육에 무리가 가지 않도록 반드시 충분한 스트레칭 후 안전하게 진행하세요.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIKTOK MASHUP VIRAL 2026 JULY PHILIPPINES 🇵🇭 </t>
+  </si>
+  <si>
+    <t>Nova Mashup</t>
+  </si>
+  <si>
+    <t>4:07</t>
+  </si>
+  <si>
+    <t>이 영상은 필리핀 지역에서 2026년 7월 기준으로 유행하는 틱톡의 인기 댄스, 밈, 챌린지 영상들을 하나로 편집한 매쉬업 콘텐츠입니다. 최신 트렌드를 한눈에 파악할 수 있도록 제작되었으며, 시청자들에게 즐거움을 선사하고 채널 구독을 독려하는 전형적인 엔터테인먼트 편집 영상입니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 자극적인 썸네일과 제목으로 조회수를 유도하는 클릭베이트성 콘텐츠일 수 있으니, 실제 영상의 질보다는 단순 오락용으로 가볍게 시청하는 것이 좋습니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lo perdió todo por culpa del amor videos viral 😱 historias completo </t>
+  </si>
+  <si>
+    <t>Wil_FFree</t>
+  </si>
+  <si>
+    <t>53:11</t>
+  </si>
+  <si>
+    <t>본 영상은 '사랑 때문에 모든 것을 잃었다'는 자극적인 제목을 내세워 시청자의 호기심을 유발하고 있습니다. 구체적인 영상 내용이나 대사가 포함되어 있지 않으며, 전형적인 클릭베이트 형식을 띠고 있어 특정 스토리텔링보다는 조회수를 목적으로 하는 바이럴 영상으로 판단됩니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 제목이 지나치게 감정적이고 자극적인 경우 실제 영상 정보가 부족한 클릭베이트일 가능성이 높으니 시청 전 주의가 필요합니다.</t>
+  </si>
+  <si>
+    <t>【大谷翔平】日本人選手が来ない…ヤ軍ブーン監督が涙の本音「謝りたい」過去の仕打ちの真相が明らかに…レジェンドも大激怒【海外の反応/MLB/メジャー/野球】</t>
+  </si>
+  <si>
+    <t>大谷翔平 SHO-TIME 【海外の反応】</t>
+  </si>
+  <si>
+    <t>17:33</t>
+  </si>
+  <si>
+    <t>뉴욕 양키스가 과거 일본인 선수들에게 가했던 비정한 처사들로 인해, 현재는 오타니 쇼헤이와 야마모토 요시노부 등 일본인 스타들이 기피하는 구단이 되었다는 내용을 담고 있습니다. 마쓰이 히데키, 이라부 히데키, 이가와 케이, 다나카 마사히로의 사례를 통해 양키스가 신뢰를 잃게 된 역사적 배경과 최근 야마모토 영입전에서 부운 감독이 겪은 어려움을 조명합니다.</t>
+  </si>
+  <si>
+    <t>⚠️해당 영상은 자극적인 제목과 썸네일을 활용하여 조회수를 유도하는 전형적인 MLB 이슈성 콘텐츠이므로 사실관계 확인이 필요합니다.</t>
   </si>
 </sst>
 </file>
@@ -395,11 +419,11 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -695,7 +719,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R9"/>
+  <dimension ref="A1:R11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:18">
@@ -780,34 +804,34 @@
         <v>24</v>
       </c>
       <c r="I2" s="3">
-        <v>142684</v>
+        <v>53315</v>
       </c>
       <c r="J2" s="3">
-        <v>2482</v>
+        <v>1187</v>
       </c>
       <c r="K2" s="3">
-        <v>158</v>
+        <v>117</v>
       </c>
       <c r="L2" s="3">
-        <v>16558</v>
+        <v>14405</v>
       </c>
       <c r="M2" s="3">
         <v>1130000</v>
       </c>
-      <c r="N2" s="4">
-        <v>0.13</v>
-      </c>
-      <c r="O2" s="5" t="s">
+      <c r="N2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="O2" s="4" t="s">
         <v>26</v>
       </c>
+      <c r="P2" s="4" t="s">
+        <v>27</v>
+      </c>
       <c r="Q2" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -824,46 +848,46 @@
         <v>2</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I3" s="3">
+        <v>26567</v>
+      </c>
+      <c r="J3" s="3">
+        <v>652</v>
+      </c>
+      <c r="K3" s="3">
+        <v>65</v>
+      </c>
+      <c r="L3" s="3">
+        <v>5881</v>
+      </c>
+      <c r="M3" s="3">
+        <v>56500</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="R3" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="I3" s="3">
-        <v>32074</v>
-      </c>
-      <c r="J3" s="3">
-        <v>850</v>
-      </c>
-      <c r="K3" s="3">
-        <v>88</v>
-      </c>
-      <c r="L3" s="3">
-        <v>15474</v>
-      </c>
-      <c r="M3" s="3">
-        <v>1130000</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="O3" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="P3" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -880,46 +904,46 @@
         <v>3</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>38</v>
       </c>
       <c r="I4" s="3">
-        <v>20013</v>
+        <v>28125</v>
       </c>
       <c r="J4" s="3">
-        <v>373</v>
+        <v>480</v>
       </c>
       <c r="K4" s="3">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="L4" s="3">
-        <v>5456</v>
+        <v>5787</v>
       </c>
       <c r="M4" s="3">
-        <v>8960</v>
+        <v>9090</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="O4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="O4" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="P4" s="5" t="s">
+      <c r="P4" s="4" t="s">
         <v>40</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -930,52 +954,52 @@
         <v>41</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D5" s="2">
         <v>1</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="I5" s="3">
+        <v>82846</v>
+      </c>
+      <c r="J5" s="3">
+        <v>1464</v>
+      </c>
+      <c r="K5" s="3">
+        <v>168</v>
+      </c>
+      <c r="L5" s="3">
+        <v>14108</v>
+      </c>
+      <c r="M5" s="3">
+        <v>173000</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="O5" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="I5" s="3">
-        <v>53895</v>
-      </c>
-      <c r="J5" s="3">
-        <v>452</v>
-      </c>
-      <c r="K5" s="3">
-        <v>199</v>
-      </c>
-      <c r="L5" s="3">
-        <v>7197</v>
-      </c>
-      <c r="M5" s="3">
-        <v>16900</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="O5" s="5" t="s">
+      <c r="P5" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="P5" s="5" t="s">
-        <v>48</v>
-      </c>
       <c r="Q5" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -983,55 +1007,55 @@
         <v>18</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D6" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>52</v>
       </c>
       <c r="I6" s="3">
-        <v>26057</v>
+        <v>35447</v>
       </c>
       <c r="J6" s="3">
-        <v>604</v>
+        <v>2424</v>
       </c>
       <c r="K6" s="3">
-        <v>94</v>
+        <v>485</v>
       </c>
       <c r="L6" s="3">
-        <v>6603</v>
+        <v>18923</v>
       </c>
       <c r="M6" s="3">
-        <v>10100</v>
+        <v>2040000</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="O6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="O6" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="P6" s="5" t="s">
+      <c r="P6" s="4" t="s">
         <v>54</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1039,13 +1063,13 @@
         <v>18</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="D7" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>55</v>
@@ -1054,40 +1078,40 @@
         <v>56</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I7" s="3">
-        <v>91165</v>
+        <v>54200</v>
       </c>
       <c r="J7" s="3">
-        <v>4042</v>
+        <v>453</v>
       </c>
       <c r="K7" s="3">
-        <v>948</v>
+        <v>198</v>
       </c>
       <c r="L7" s="3">
-        <v>34885</v>
+        <v>6640</v>
       </c>
       <c r="M7" s="3">
-        <v>1170000</v>
+        <v>16900</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="O7" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="P7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="O7" s="4" t="s">
         <v>59</v>
       </c>
+      <c r="P7" s="4" t="s">
+        <v>60</v>
+      </c>
       <c r="Q7" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1095,55 +1119,55 @@
         <v>18</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="D8" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I8" s="3">
-        <v>21041</v>
+        <v>30951</v>
       </c>
       <c r="J8" s="3">
-        <v>724</v>
+        <v>778</v>
       </c>
       <c r="K8" s="3">
-        <v>187</v>
+        <v>109</v>
       </c>
       <c r="L8" s="3">
-        <v>4790</v>
+        <v>6594</v>
       </c>
       <c r="M8" s="3">
-        <v>1210000</v>
+        <v>10300</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="O8" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="P8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="O8" s="4" t="s">
         <v>64</v>
       </c>
+      <c r="P8" s="4" t="s">
+        <v>65</v>
+      </c>
       <c r="Q8" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1151,55 +1175,167 @@
         <v>18</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D9" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>68</v>
       </c>
       <c r="I9" s="3">
-        <v>21072</v>
+        <v>95163</v>
       </c>
       <c r="J9" s="3">
-        <v>602</v>
+        <v>4113</v>
       </c>
       <c r="K9" s="3">
-        <v>52</v>
+        <v>939</v>
       </c>
       <c r="L9" s="3">
-        <v>3678</v>
+        <v>29878</v>
       </c>
       <c r="M9" s="3">
-        <v>41900</v>
+        <v>1170000</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="O9" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="O9" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="P9" s="5" t="s">
+      <c r="P9" s="4" t="s">
         <v>70</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R9" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
+      <c r="A10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="2">
+        <v>2</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="I10" s="3">
+        <v>21692</v>
+      </c>
+      <c r="J10" s="3">
+        <v>2160</v>
+      </c>
+      <c r="K10" s="3">
+        <v>642</v>
+      </c>
+      <c r="L10" s="3">
+        <v>21130</v>
+      </c>
+      <c r="M10" s="3">
+        <v>94100</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="O10" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="P10" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q10" s="2" t="s">
         <v>28</v>
+      </c>
+      <c r="R10" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
+      <c r="A11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="2">
+        <v>3</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I11" s="3">
+        <v>37014</v>
+      </c>
+      <c r="J11" s="3">
+        <v>3231</v>
+      </c>
+      <c r="K11" s="3">
+        <v>495</v>
+      </c>
+      <c r="L11" s="3">
+        <v>12280</v>
+      </c>
+      <c r="M11" s="3">
+        <v>1170000</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="O11" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="P11" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1212,6 +1348,8 @@
     <hyperlink ref="Q7" r:id="rId6"/>
     <hyperlink ref="Q8" r:id="rId7"/>
     <hyperlink ref="Q9" r:id="rId8"/>
+    <hyperlink ref="Q10" r:id="rId9"/>
+    <hyperlink ref="Q11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1286,52 +1424,52 @@
         <v>41</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="I2" s="3">
-        <v>69419</v>
+        <v>91328</v>
       </c>
       <c r="J2" s="3">
-        <v>1008</v>
+        <v>1863</v>
       </c>
       <c r="K2" s="3">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="L2" s="3">
         <v>0</v>
       </c>
       <c r="M2" s="3">
-        <v>401</v>
-      </c>
-      <c r="N2" s="4">
-        <v>173</v>
-      </c>
-      <c r="O2" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="P2" s="5" t="s">
-        <v>76</v>
+        <v>728</v>
+      </c>
+      <c r="N2" s="5">
+        <v>125</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>85</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1339,55 +1477,55 @@
         <v>18</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="D3" s="2">
         <v>2</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I3" s="3">
-        <v>100660</v>
+        <v>74957</v>
       </c>
       <c r="J3" s="3">
-        <v>855</v>
+        <v>407</v>
       </c>
       <c r="K3" s="3">
-        <v>67</v>
+        <v>3</v>
       </c>
       <c r="L3" s="3">
         <v>0</v>
       </c>
       <c r="M3" s="3">
-        <v>598</v>
-      </c>
-      <c r="N3" s="4">
-        <v>168</v>
-      </c>
-      <c r="O3" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="P3" s="5" t="s">
-        <v>82</v>
+        <v>872</v>
+      </c>
+      <c r="N3" s="5">
+        <v>86</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>90</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1395,55 +1533,55 @@
         <v>18</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="D4" s="2">
         <v>3</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="I4" s="3">
-        <v>85005</v>
+        <v>58578</v>
       </c>
       <c r="J4" s="3">
-        <v>788</v>
+        <v>119</v>
       </c>
       <c r="K4" s="3">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="L4" s="3">
         <v>0</v>
       </c>
       <c r="M4" s="3">
-        <v>509</v>
-      </c>
-      <c r="N4" s="4">
-        <v>167</v>
-      </c>
-      <c r="O4" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="P4" s="5" t="s">
-        <v>87</v>
+        <v>737</v>
+      </c>
+      <c r="N4" s="5">
+        <v>79</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>95</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1451,55 +1589,55 @@
         <v>18</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="D5" s="2">
         <v>4</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="I5" s="3">
-        <v>51346</v>
+        <v>130259</v>
       </c>
       <c r="J5" s="3">
-        <v>887</v>
+        <v>1099</v>
       </c>
       <c r="K5" s="3">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="L5" s="3">
         <v>0</v>
       </c>
       <c r="M5" s="3">
-        <v>727</v>
-      </c>
-      <c r="N5" s="4">
-        <v>71</v>
-      </c>
-      <c r="O5" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="P5" s="5" t="s">
-        <v>92</v>
+        <v>4020</v>
+      </c>
+      <c r="N5" s="5">
+        <v>32</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="P5" s="4" t="s">
+        <v>100</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1507,55 +1645,55 @@
         <v>18</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>77</v>
+        <v>41</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="D6" s="2">
         <v>5</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="I6" s="3">
-        <v>52499</v>
+        <v>121417</v>
       </c>
       <c r="J6" s="3">
-        <v>527</v>
+        <v>895</v>
       </c>
       <c r="K6" s="3">
-        <v>6</v>
+        <v>301</v>
       </c>
       <c r="L6" s="3">
         <v>0</v>
       </c>
       <c r="M6" s="3">
-        <v>1250</v>
-      </c>
-      <c r="N6" s="4">
-        <v>42</v>
-      </c>
-      <c r="O6" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="P6" s="5" t="s">
-        <v>97</v>
+        <v>9680</v>
+      </c>
+      <c r="N6" s="5">
+        <v>13</v>
+      </c>
+      <c r="O6" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="P6" s="4" t="s">
+        <v>105</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
